--- a/partner_results/unknown_complete/ClassesWithMultipleGermanLabels_unknown.xlsx
+++ b/partner_results/unknown_complete/ClassesWithMultipleGermanLabels_unknown.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Datenverarbeitung | Rechenprozess</t>
+          <t>Rechenprozess | Datenverarbeitung</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
